--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Observation profile for contact mode at three-month follow-up.</t>
+    <t>Observation profile for the modality used to obtain three-month follow-up information.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -715,7 +715,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -792,7 +792,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Three-month contact mode</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -833,10 +833,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -887,10 +887,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1790,98 +1790,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2075,10 +2077,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2160,7 +2162,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/three-month-contact-mode-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/three-month-contact-mode-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/base-stroke-observation</t>
+    <t>http://qualityregistry.org/StructureDefinition/base-stroke-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -804,7 +804,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/three-month-contact-mode-vs</t>
+    <t>http://qualityregistry.org/ValueSet/three-month-contact-mode-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -829,7 +829,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -883,7 +883,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
+++ b/StructureDefinition-three-month-contact-mode-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
